--- a/storage/vorlage/projekte/bop/excel/Anwesenheitsliste-Vorbereitung-BO-Tage.xlsx
+++ b/storage/vorlage/projekte/bop/excel/Anwesenheitsliste-Vorbereitung-BO-Tage.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\bop\storage\vorlage\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\zbb\storage\vorlage\projekte\bop\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1970,7 +1970,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.78740157480314965" right="0.98425196850393704" top="0.78740157480314965" bottom="1.5748031496062993" header="0.31496062992125984" footer="0"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;RSeite &amp;P von &amp;N</oddHeader>
     <oddFooter>&amp;L&amp;G</oddFooter>
